--- a/public/templates/test_input/baocaocongtruong_khaithac_21.xlsx
+++ b/public/templates/test_input/baocaocongtruong_khaithac_21.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="0" windowWidth="18795" windowHeight="10905" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>CT Khai thác 1</t>
+          <t>Khai thác 2</t>
         </is>
       </c>
       <c r="C5" s="69" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>CT Khai thác 1</t>
+          <t>Khai thác 1</t>
         </is>
       </c>
       <c r="C8" s="69" t="n">
@@ -1822,7 +1822,7 @@
       <c r="A11" s="70" t="n"/>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>CT Khai thác 2</t>
+          <t>Khai thác 8</t>
         </is>
       </c>
       <c r="C11" s="69" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>CT Khai thác 1</t>
+          <t>Khai thác 6</t>
         </is>
       </c>
       <c r="C14" s="69" t="n">
